--- a/boss_pack/target_table.xlsx
+++ b/boss_pack/target_table.xlsx
@@ -107,7 +107,7 @@
     <col min="7" max="7" width="25" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="35" customWidth="1"/>
-    <col min="10" max="10" width="38" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
     <col min="12" max="12" width="42" customWidth="1"/>
     <col min="13" max="13" width="42" customWidth="1"/>
@@ -179,7 +179,7 @@
       </c>
       <c r="J3" t="inlineStr" s="2">
         <is>
-          <t>Gics Industry Group</t>
+          <t>Subsector</t>
         </is>
       </c>
       <c r="K3" t="inlineStr" s="2">
@@ -255,27 +255,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Businesses</t>
+          <t>Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Homecare &amp; nursing agencies</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>public profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -341,7 +341,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -422,7 +422,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Plumbing &amp; drainage</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Steel fabrication &amp; metalwork</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -741,27 +741,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>public profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Plant &amp; equipment maintenance</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Commercial Nurseries</t>
+          <t>Retail &amp; Consumer</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Garden centres &amp; nurseries</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Plumbing &amp; drainage</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Steel fabrication &amp; metalwork</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2118,27 +2118,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>agri_food</t>
+          <t>Food &amp; Agribusiness</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Agricultural supply &amp; co-ops</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>public profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Landscaping / Grounds Services</t>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Landscaping &amp; grounds maintenance</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Landscaping / Grounds Services</t>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Landscaping &amp; grounds maintenance</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Dental practices</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Dental practices</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Furniture &amp; interiors</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Dental practices</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Life Sciences</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>GP &amp; primary care practices</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>GP &amp; primary care practices</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Media &amp; Creative</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Mortgage broking &amp; financial advisory</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Transport &amp; Logistics</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Landscaping / Grounds Services</t>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Landscaping &amp; grounds maintenance</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Furniture &amp; interiors</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Solicitors &amp; legal practices</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Life Sciences</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Dental practices</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Dental practices</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Steel fabrication &amp; metalwork</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Transport &amp; Logistics</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Garden centres &amp; nurseries</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Road haulage &amp; freight</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Printing &amp; signage</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Transport &amp; Logistics</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Transport &amp; Logistics</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Physiotherapy &amp; rehabilitation</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Fit-out &amp; refurbishment</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Hardware &amp; DIY</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Car wash &amp; valeting</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Hotels &amp; guesthouses</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -9732,12 +9732,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t/>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -10056,12 +10056,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Playschools</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Butchers &amp; artisan food producers</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -10785,12 +10785,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Accounting &amp; bookkeeping practices</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Event venues &amp; catering</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Security &amp; guarding services</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -12405,12 +12405,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Tyre &amp; exhaust centres</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Furniture &amp; interiors</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Event venues &amp; catering</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -13539,12 +13539,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -13620,12 +13620,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -13701,12 +13701,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Motor repair &amp; servicing garages</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -14673,12 +14673,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -14754,12 +14754,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -14921,7 +14921,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -15159,12 +15159,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Hotels &amp; guesthouses</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -15650,7 +15650,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Security &amp; guarding services</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -16050,12 +16050,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -16136,7 +16136,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Tyre &amp; exhaust centres</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -16217,7 +16217,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -16865,7 +16865,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -16946,7 +16946,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -17022,12 +17022,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -17513,7 +17513,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -17589,12 +17589,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -17675,7 +17675,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Hotels &amp; guesthouses</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -17837,7 +17837,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>PR &amp; marketing agencies</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -18156,12 +18156,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Hotels &amp; guesthouses</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -18485,7 +18485,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -18561,12 +18561,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t/>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -18885,12 +18885,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -18966,12 +18966,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Security &amp; guarding services</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -19376,7 +19376,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -19499,66 +19499,66 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A. O'TOOLE (CONFECTIONERS) LIMITED</t>
+          <t>Successful Pizza Business In North Dublin</t>
         </is>
       </c>
       <c r="B242">
-        <v>24.4</v>
+        <v>19.9</v>
       </c>
       <c r="C242">
-        <v>24.4</v>
+        <v>41.9</v>
       </c>
       <c r="D242">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -19573,33 +19573,33 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>ic_packs/cro-72100/watch_note.md</t>
+          <t>ic_packs/name-county-successful-pizza-business-in-north-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Bonordic in Dublin</t>
+          <t>The Cappuccino Bar</t>
         </is>
       </c>
       <c r="B243">
-        <v>23.6</v>
+        <v>19.9</v>
       </c>
       <c r="C243">
-        <v>23.6</v>
+        <v>41.9</v>
       </c>
       <c r="D243">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -19629,12 +19629,12 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -19654,33 +19654,33 @@
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-bonordic-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-cappuccino-bar-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Brian Tracy Solutions Leadership &amp; Sales Training Consultancy in Galway</t>
+          <t>Coworking Master License Opportunity In Ireland</t>
         </is>
       </c>
       <c r="B244">
-        <v>23.6</v>
+        <v>19.3</v>
       </c>
       <c r="C244">
-        <v>23.6</v>
+        <v>41.3</v>
       </c>
       <c r="D244">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -19700,7 +19700,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -19735,43 +19735,43 @@
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-brian-tracy-solutions-leadership-sales-training-consultancy-in-galway-galway/watch_note.md</t>
+          <t>ic_packs/name-county-coworking-master-license-opportunity-in-ireland-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Brian Tracy Solutions Leadership &amp; Sales Training Consultancy in Swords</t>
+          <t>5SRE 5 STAR REAL ESTATE LIMITED</t>
         </is>
       </c>
       <c r="B245">
-        <v>23.6</v>
+        <v>18.4</v>
       </c>
       <c r="C245">
-        <v>23.6</v>
+        <v>40.4</v>
       </c>
       <c r="D245">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -19781,27 +19781,27 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -19816,43 +19816,43 @@
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-brian-tracy-solutions-leadership-sales-training-consultancy-in-swords-dublin/watch_note.md</t>
+          <t>ic_packs/cro-718110/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Energie fitness in Dublin</t>
+          <t>9TH IMPACT LIMITED</t>
         </is>
       </c>
       <c r="B246">
-        <v>23.6</v>
+        <v>18.4</v>
       </c>
       <c r="C246">
-        <v>23.6</v>
+        <v>40.4</v>
       </c>
       <c r="D246">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -19862,27 +19862,27 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
@@ -19897,33 +19897,33 @@
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-energie-fitness-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-552335/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Energie fitness in Swords</t>
+          <t>Bonordic in Galway</t>
         </is>
       </c>
       <c r="B247">
-        <v>23.6</v>
+        <v>18.4</v>
       </c>
       <c r="C247">
-        <v>23.6</v>
+        <v>40.4</v>
       </c>
       <c r="D247">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -19978,33 +19978,33 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-energie-fitness-in-swords-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-bonordic-in-galway-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Young Engineers Franchise in Dublin</t>
+          <t>Greenfeet Lawn Care Franchise in South Dublin</t>
         </is>
       </c>
       <c r="B248">
-        <v>23.6</v>
+        <v>17.7</v>
       </c>
       <c r="C248">
-        <v>23.6</v>
+        <v>39.7</v>
       </c>
       <c r="D248">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20059,73 +20059,73 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-young-engineers-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-greenfeet-lawn-care-franchise-in-south-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>(POLYCRAFTS IRELAND LIMITED) OLL CHEARD EIRE TEORANTA</t>
+          <t>Activewear Brand Online Business</t>
         </is>
       </c>
       <c r="B249">
-        <v>23.1</v>
+        <v>17.3</v>
       </c>
       <c r="C249">
-        <v>23.1</v>
+        <v>39.3</v>
       </c>
       <c r="D249">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -20140,38 +20140,38 @@
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>ic_packs/cro-106973/watch_note.md</t>
+          <t>ic_packs/name-county-activewear-brand-online-business-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2TYPE3 SUSTAINABILITY PARTNERS LIMITED</t>
+          <t>Established Pizzeria Killarney</t>
         </is>
       </c>
       <c r="B250">
-        <v>23.1</v>
+        <v>17.3</v>
       </c>
       <c r="C250">
-        <v>23.1</v>
+        <v>39.3</v>
       </c>
       <c r="D250">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -20181,32 +20181,32 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t/>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -20221,73 +20221,73 @@
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>ic_packs/cro-462330/watch_note.md</t>
+          <t>ic_packs/name-county-established-pizzeria-killarney-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>36 O'CONNELL STREET MANAGEMENT LIMITED</t>
+          <t>Established Tyre Shop/Service Business</t>
         </is>
       </c>
       <c r="B251">
-        <v>23.1</v>
+        <v>17.3</v>
       </c>
       <c r="C251">
-        <v>23.1</v>
+        <v>39.3</v>
       </c>
       <c r="D251">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t/>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Tyre &amp; exhaust centres</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -20302,73 +20302,73 @@
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>ic_packs/cro-360393/watch_note.md</t>
+          <t>ic_packs/name-county-established-tyre-shop-service-business-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3D VENTURES LIMITED</t>
+          <t>Turnkey Hair Salon For Sale in Dublin 24</t>
         </is>
       </c>
       <c r="B252">
-        <v>23.1</v>
+        <v>17.3</v>
       </c>
       <c r="C252">
-        <v>23.1</v>
+        <v>39.3</v>
       </c>
       <c r="D252">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t/>
+          <t>Retail &amp; Consumer</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
@@ -20383,73 +20383,73 @@
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>ic_packs/cro-470032/watch_note.md</t>
+          <t>ic_packs/name-county-turnkey-hair-salon-for-sale-in-dublin-24-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A &amp; M. DISTRIBUTORS LIMITED</t>
+          <t>Commercial Kitchen And Food Production Facility</t>
         </is>
       </c>
       <c r="B253">
-        <v>23.1</v>
+        <v>16.6</v>
       </c>
       <c r="C253">
-        <v>23.1</v>
+        <v>38.6</v>
       </c>
       <c r="D253">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -20464,73 +20464,73 @@
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>ic_packs/cro-226593/watch_note.md</t>
+          <t>ic_packs/name-county-commercial-kitchen-and-food-production-facility-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A &amp; P AVIATION LIMITED</t>
+          <t>E-commerce Store l €1200PM Profits</t>
         </is>
       </c>
       <c r="B254">
-        <v>23.1</v>
+        <v>16.6</v>
       </c>
       <c r="C254">
-        <v>23.1</v>
+        <v>38.6</v>
       </c>
       <c r="D254">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -20545,73 +20545,73 @@
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>ic_packs/cro-189250/watch_note.md</t>
+          <t>ic_packs/name-county-e-commerce-store-l-1200pm-profits-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A. B. C. CUISINES LIMITED</t>
+          <t>Exceptional Restaurant, Takeaway</t>
         </is>
       </c>
       <c r="B255">
-        <v>23.1</v>
+        <v>16.6</v>
       </c>
       <c r="C255">
-        <v>23.1</v>
+        <v>38.6</v>
       </c>
       <c r="D255">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t/>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -20626,38 +20626,38 @@
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>ic_packs/cro-58944/watch_note.md</t>
+          <t>ic_packs/name-county-exceptional-restaurant-takeaway-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A. G. FEED LIMITED</t>
+          <t>Woodford Garden Centre</t>
         </is>
       </c>
       <c r="B256">
-        <v>23.1</v>
+        <v>16.6</v>
       </c>
       <c r="C256">
-        <v>23.1</v>
+        <v>38.6</v>
       </c>
       <c r="D256">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -20667,32 +20667,32 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t/>
+          <t>Retail &amp; Consumer</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Garden centres &amp; nurseries</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -20707,73 +20707,73 @@
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>ic_packs/cro-347425/watch_note.md</t>
+          <t>ic_packs/name-county-woodford-garden-centre-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A. K. D. LIMITED</t>
+          <t>GPS Device Franchise Opportunity</t>
         </is>
       </c>
       <c r="B257">
-        <v>23.1</v>
+        <v>15.8</v>
       </c>
       <c r="C257">
-        <v>23.1</v>
+        <v>37.8</v>
       </c>
       <c r="D257">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -20788,33 +20788,33 @@
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>ic_packs/cro-75533/watch_note.md</t>
+          <t>ic_packs/name-county-gps-device-franchise-opportunity-ireland/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A. LOOK LIMITED</t>
+          <t>A &amp; S ROOFING &amp; FLOORING LIMITED</t>
         </is>
       </c>
       <c r="B258">
-        <v>23.1</v>
+        <v>15.0</v>
       </c>
       <c r="C258">
-        <v>23.1</v>
+        <v>37.0</v>
       </c>
       <c r="D258">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -20829,12 +20829,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -20869,33 +20869,33 @@
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>ic_packs/cro-322344/watch_note.md</t>
+          <t>ic_packs/cro-89969/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A.1. DEV CHIMNEY CO. LIMITED</t>
+          <t>A B P MANUFACTURING MACHINERY LIMITED</t>
         </is>
       </c>
       <c r="B259">
-        <v>23.1</v>
+        <v>15.0</v>
       </c>
       <c r="C259">
-        <v>23.1</v>
+        <v>37.0</v>
       </c>
       <c r="D259">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -20910,12 +20910,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t/>
+          <t>Industrials &amp; Engineering</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -20950,33 +20950,33 @@
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>ic_packs/cro-346214/watch_note.md</t>
+          <t>ic_packs/cro-463722/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A.B.V.G. (A BRIGHTER VISION GENERALLY) LIMITED</t>
+          <t>A.1. BUILDERS LIMITED</t>
         </is>
       </c>
       <c r="B260">
-        <v>23.1</v>
+        <v>15.0</v>
       </c>
       <c r="C260">
-        <v>23.1</v>
+        <v>37.0</v>
       </c>
       <c r="D260">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -20991,12 +20991,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -21016,7 +21016,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -21031,73 +21031,73 @@
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>ic_packs/cro-465159/watch_note.md</t>
+          <t>ic_packs/cro-129924/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A.E.R. LIMITED</t>
+          <t>Filling Stations</t>
         </is>
       </c>
       <c r="B261">
-        <v>23.1</v>
+        <v>13.9</v>
       </c>
       <c r="C261">
-        <v>23.1</v>
+        <v>35.9</v>
       </c>
       <c r="D261">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -21112,73 +21112,73 @@
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>ic_packs/cro-240545/watch_note.md</t>
+          <t>ic_packs/name-county-filling-stations-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A.M. &amp; D. LIMITED</t>
+          <t>Profitable And High Potential Natural Juices Business Ireland</t>
         </is>
       </c>
       <c r="B262">
-        <v>23.1</v>
+        <v>13.9</v>
       </c>
       <c r="C262">
-        <v>23.1</v>
+        <v>35.9</v>
       </c>
       <c r="D262">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -21193,33 +21193,33 @@
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>ic_packs/cro-214417/watch_note.md</t>
+          <t>ic_packs/name-county-profitable-and-high-potential-natural-juices-business-ireland-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A.M.T. GALWAY LIMITED</t>
+          <t>A.P. MCCARTHY PLANNING CONSULTANTS LIMITED</t>
         </is>
       </c>
       <c r="B263">
-        <v>23.1</v>
+        <v>13.7</v>
       </c>
       <c r="C263">
-        <v>23.1</v>
+        <v>35.7</v>
       </c>
       <c r="D263">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -21234,12 +21234,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -21274,33 +21274,33 @@
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>ic_packs/cro-162537/watch_note.md</t>
+          <t>ic_packs/cro-328511/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>GARDEN LEISURE PRODUCTS LIMITED/TROSCAN GHAIRDINI TEORANTA</t>
+          <t>A. M. S. ENGINEERING COMPANY LIMITED</t>
         </is>
       </c>
       <c r="B264">
-        <v>23.1</v>
+        <v>12.3</v>
       </c>
       <c r="C264">
-        <v>23.1</v>
+        <v>34.3</v>
       </c>
       <c r="D264">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -21315,12 +21315,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t/>
+          <t>Industrials &amp; Engineering</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -21355,73 +21355,73 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>ic_packs/cro-157217/watch_note.md</t>
+          <t>ic_packs/cro-28525/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>GARDEN PRIDE TOOL HIRE LIMITED</t>
+          <t>Surveillance Device Sales Partner Opportunity</t>
         </is>
       </c>
       <c r="B265">
-        <v>23.1</v>
+        <v>11.6</v>
       </c>
       <c r="C265">
-        <v>23.1</v>
+        <v>33.6</v>
       </c>
       <c r="D265">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t/>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -21436,33 +21436,33 @@
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>ic_packs/cro-369982/watch_note.md</t>
+          <t>ic_packs/name-county-surveillance-device-sales-partner-opportunity-ireland/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>LAWN RANGER LIMITED</t>
+          <t>A &amp; D; ADVERTISING AND DESIGN CONSULTANTS LIMITED</t>
         </is>
       </c>
       <c r="B266">
-        <v>23.1</v>
+        <v>11.0</v>
       </c>
       <c r="C266">
-        <v>23.1</v>
+        <v>33.0</v>
       </c>
       <c r="D266">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -21477,12 +21477,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -21502,7 +21502,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -21517,33 +21517,33 @@
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>ic_packs/cro-345282/watch_note.md</t>
+          <t>ic_packs/cro-234849/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>40 DEGREES LIMITED</t>
+          <t>A LEONARD MANAGEMENT &amp; CONSULTING LIMITED</t>
         </is>
       </c>
       <c r="B267">
-        <v>21.0</v>
+        <v>11.0</v>
       </c>
       <c r="C267">
-        <v>21.0</v>
+        <v>33.0</v>
       </c>
       <c r="D267">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -21558,12 +21558,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -21598,33 +21598,33 @@
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>ic_packs/cro-270945/watch_note.md</t>
+          <t>ic_packs/cro-481667/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4D SOFTWARE LIMITED</t>
+          <t>GROUNDSOURCE LIMITED</t>
         </is>
       </c>
       <c r="B268">
-        <v>21.0</v>
+        <v>10.1</v>
       </c>
       <c r="C268">
-        <v>21.0</v>
+        <v>32.1</v>
       </c>
       <c r="D268">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -21639,12 +21639,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -21679,73 +21679,73 @@
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>ic_packs/cro-406809/watch_note.md</t>
+          <t>ic_packs/cro-385921/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A J D DEVELOPMENTS LIMITED</t>
+          <t>KD ECO+ Laminates - Services Franchise in Dublin</t>
         </is>
       </c>
       <c r="B269">
-        <v>21.0</v>
+        <v>9.7</v>
       </c>
       <c r="C269">
-        <v>21.0</v>
+        <v>31.7</v>
       </c>
       <c r="D269">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -21760,38 +21760,38 @@
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>ic_packs/cro-328171/watch_note.md</t>
+          <t>ic_packs/name-county-kd-eco-laminates-services-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A.M. &amp; D. HOLDINGS LIMITED</t>
+          <t>KD ECO+ Laminates - Services Franchise in Galway</t>
         </is>
       </c>
       <c r="B270">
-        <v>21.0</v>
+        <v>9.7</v>
       </c>
       <c r="C270">
-        <v>21.0</v>
+        <v>31.7</v>
       </c>
       <c r="D270">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -21801,32 +21801,32 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -21841,21 +21841,21 @@
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>ic_packs/cro-217915/watch_note.md</t>
+          <t>ic_packs/name-county-kd-eco-laminates-services-franchise-in-galway-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Successful Pizza Business In North Dublin</t>
+          <t>A.E.D. SECURITY INSTALLATIONS LIMITED</t>
         </is>
       </c>
       <c r="B271">
-        <v>19.9</v>
+        <v>8.4</v>
       </c>
       <c r="C271">
-        <v>41.9</v>
+        <v>30.4</v>
       </c>
       <c r="D271">
         <v>22.0</v>
@@ -21872,12 +21872,12 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -21887,22 +21887,22 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -21922,21 +21922,21 @@
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-successful-pizza-business-in-north-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-359827/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>The Cappuccino Bar</t>
+          <t>High End Pizza Franchise - Only €5,000</t>
         </is>
       </c>
       <c r="B272">
-        <v>19.9</v>
+        <v>7.6</v>
       </c>
       <c r="C272">
-        <v>41.9</v>
+        <v>29.6</v>
       </c>
       <c r="D272">
         <v>22.0</v>
@@ -21963,12 +21963,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -22003,21 +22003,21 @@
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-cappuccino-bar-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-high-end-pizza-franchise-only-5-000-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Coworking Master License Opportunity In Ireland</t>
+          <t>Gym Franchise Opportunity</t>
         </is>
       </c>
       <c r="B273">
-        <v>19.3</v>
+        <v>7.2</v>
       </c>
       <c r="C273">
-        <v>41.3</v>
+        <v>29.2</v>
       </c>
       <c r="D273">
         <v>22.0</v>
@@ -22039,7 +22039,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -22059,12 +22059,12 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -22084,21 +22084,21 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-coworking-master-license-opportunity-in-ireland-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-gym-franchise-opportunity-ireland/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5SRE 5 STAR REAL ESTATE LIMITED</t>
+          <t>Best.Energy - Energy Monitoring Franchise in Dublin</t>
         </is>
       </c>
       <c r="B274">
-        <v>18.4</v>
+        <v>7.0</v>
       </c>
       <c r="C274">
-        <v>40.4</v>
+        <v>29.0</v>
       </c>
       <c r="D274">
         <v>22.0</v>
@@ -22115,42 +22115,42 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -22165,21 +22165,21 @@
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>ic_packs/cro-718110/watch_note.md</t>
+          <t>ic_packs/name-county-best-energy-energy-monitoring-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>9TH IMPACT LIMITED</t>
+          <t>Franchise Pizzeria Restaurant l 3 Bed Apartment Galway</t>
         </is>
       </c>
       <c r="B275">
-        <v>18.4</v>
+        <v>6.7</v>
       </c>
       <c r="C275">
-        <v>40.4</v>
+        <v>28.7</v>
       </c>
       <c r="D275">
         <v>22.0</v>
@@ -22196,7 +22196,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -22206,32 +22206,32 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t/>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -22246,21 +22246,21 @@
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>ic_packs/cro-552335/watch_note.md</t>
+          <t>ic_packs/name-county-franchise-pizzeria-restaurant-l-3-bed-apartment-galway-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Bonordic in Galway</t>
+          <t>(NEW AGE OFFICE FURNITURE LIMITED) TROSCAN OIFIGE NA H'AOISE NUA TEORANTA</t>
         </is>
       </c>
       <c r="B276">
-        <v>18.4</v>
+        <v>6.4</v>
       </c>
       <c r="C276">
-        <v>40.4</v>
+        <v>28.4</v>
       </c>
       <c r="D276">
         <v>22.0</v>
@@ -22277,7 +22277,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -22292,27 +22292,27 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Furniture &amp; interiors</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -22327,21 +22327,21 @@
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-bonordic-in-galway-galway/watch_note.md</t>
+          <t>ic_packs/cro-154946/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Greenfeet Lawn Care Franchise in South Dublin</t>
+          <t>Multi-Site Fitness Franchise Portfolio – Ireland</t>
         </is>
       </c>
       <c r="B277">
-        <v>17.7</v>
+        <v>5.0</v>
       </c>
       <c r="C277">
-        <v>39.7</v>
+        <v>27.0</v>
       </c>
       <c r="D277">
         <v>22.0</v>
@@ -22368,12 +22368,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -22408,21 +22408,21 @@
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-greenfeet-lawn-care-franchise-in-south-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-multi-site-fitness-franchise-portfolio-ireland-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Activewear Brand Online Business</t>
+          <t>Evoglide Automotive Franchise in Dublin</t>
         </is>
       </c>
       <c r="B278">
-        <v>17.3</v>
+        <v>4.3</v>
       </c>
       <c r="C278">
-        <v>39.3</v>
+        <v>26.3</v>
       </c>
       <c r="D278">
         <v>22.0</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -22489,21 +22489,21 @@
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-activewear-brand-online-business-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-evoglide-automotive-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Established Pizzeria Killarney</t>
+          <t>Four Star Pizza in Balbriggan</t>
         </is>
       </c>
       <c r="B279">
-        <v>17.3</v>
+        <v>4.3</v>
       </c>
       <c r="C279">
-        <v>39.3</v>
+        <v>26.3</v>
       </c>
       <c r="D279">
         <v>22.0</v>
@@ -22525,17 +22525,17 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -22570,21 +22570,21 @@
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-established-pizzeria-killarney-galway/watch_note.md</t>
+          <t>ic_packs/name-county-four-star-pizza-in-balbriggan-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Established Tyre Shop/Service Business</t>
+          <t>Gecko Hospitality Recruitment Franchise in Dublin</t>
         </is>
       </c>
       <c r="B280">
-        <v>17.3</v>
+        <v>4.3</v>
       </c>
       <c r="C280">
-        <v>39.3</v>
+        <v>26.3</v>
       </c>
       <c r="D280">
         <v>22.0</v>
@@ -22611,12 +22611,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Recruitment &amp; staffing agencies</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -22651,21 +22651,21 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-established-tyre-shop-service-business-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-gecko-hospitality-recruitment-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Turnkey Hair Salon For Sale in Dublin 24</t>
+          <t>Signarama International Master Franchise Opportunities</t>
         </is>
       </c>
       <c r="B281">
-        <v>17.3</v>
+        <v>4.3</v>
       </c>
       <c r="C281">
-        <v>39.3</v>
+        <v>26.3</v>
       </c>
       <c r="D281">
         <v>22.0</v>
@@ -22692,12 +22692,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -22732,21 +22732,21 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-turnkey-hair-salon-for-sale-in-dublin-24-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-signarama-international-master-franchise-opportunities-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Commercial Kitchen And Food Production Facility</t>
+          <t>Specialist Glass Repairs - Glass &amp; Acrylic Repair Franchise in Dublin</t>
         </is>
       </c>
       <c r="B282">
-        <v>16.6</v>
+        <v>4.3</v>
       </c>
       <c r="C282">
-        <v>38.6</v>
+        <v>26.3</v>
       </c>
       <c r="D282">
         <v>22.0</v>
@@ -22778,7 +22778,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -22813,21 +22813,21 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-commercial-kitchen-and-food-production-facility-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-specialist-glass-repairs-glass-acrylic-repair-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>E-commerce Store l €1200PM Profits</t>
+          <t>WeddingBox Event Planning Franchise in Dublin</t>
         </is>
       </c>
       <c r="B283">
-        <v>16.6</v>
+        <v>4.3</v>
       </c>
       <c r="C283">
-        <v>38.6</v>
+        <v>26.3</v>
       </c>
       <c r="D283">
         <v>22.0</v>
@@ -22854,12 +22854,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -22894,21 +22894,21 @@
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-e-commerce-store-l-1200pm-profits-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-weddingbox-event-planning-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Exceptional Restaurant, Takeaway</t>
+          <t>GARDEN GREEN ENERGY LIMITED</t>
         </is>
       </c>
       <c r="B284">
-        <v>16.6</v>
+        <v>3.8</v>
       </c>
       <c r="C284">
-        <v>38.6</v>
+        <v>25.8</v>
       </c>
       <c r="D284">
         <v>22.0</v>
@@ -22925,42 +22925,42 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
@@ -22975,38 +22975,38 @@
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-exceptional-restaurant-takeaway-dublin/watch_note.md</t>
+          <t>ic_packs/cro-463334/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Woodford Garden Centre</t>
+          <t>(POLYCRAFTS IRELAND LIMITED) OLL CHEARD EIRE TEORANTA</t>
         </is>
       </c>
       <c r="B285">
-        <v>16.6</v>
+        <v>0.0</v>
       </c>
       <c r="C285">
-        <v>38.6</v>
+        <v>23.1</v>
       </c>
       <c r="D285">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -23016,32 +23016,32 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -23056,73 +23056,73 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-woodford-garden-centre-galway/watch_note.md</t>
+          <t>ic_packs/cro-106973/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>GPS Device Franchise Opportunity</t>
+          <t>2TYPE3 SUSTAINABILITY PARTNERS LIMITED</t>
         </is>
       </c>
       <c r="B286">
-        <v>15.8</v>
+        <v>0.0</v>
       </c>
       <c r="C286">
-        <v>37.8</v>
+        <v>23.1</v>
       </c>
       <c r="D286">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Transport &amp; Logistics</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
@@ -23137,33 +23137,33 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-gps-device-franchise-opportunity-ireland/watch_note.md</t>
+          <t>ic_packs/cro-462330/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>A &amp; S ROOFING &amp; FLOORING LIMITED</t>
+          <t>36 O'CONNELL STREET MANAGEMENT LIMITED</t>
         </is>
       </c>
       <c r="B287">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="C287">
-        <v>37.0</v>
+        <v>23.1</v>
       </c>
       <c r="D287">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Construction Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -23203,7 +23203,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -23218,33 +23218,33 @@
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>ic_packs/cro-89969/watch_note.md</t>
+          <t>ic_packs/cro-360393/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>A B P MANUFACTURING MACHINERY LIMITED</t>
+          <t>3D VENTURES LIMITED</t>
         </is>
       </c>
       <c r="B288">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="C288">
-        <v>37.0</v>
+        <v>23.1</v>
       </c>
       <c r="D288">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -23259,12 +23259,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -23299,33 +23299,33 @@
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>ic_packs/cro-463722/watch_note.md</t>
+          <t>ic_packs/cro-470032/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>A.1. BUILDERS LIMITED</t>
+          <t>40 DEGREES LIMITED</t>
         </is>
       </c>
       <c r="B289">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="C289">
-        <v>37.0</v>
+        <v>21.0</v>
       </c>
       <c r="D289">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -23340,12 +23340,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Construction Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23365,7 +23365,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -23380,73 +23380,73 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>ic_packs/cro-129924/watch_note.md</t>
+          <t>ic_packs/cro-270945/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Filling Stations</t>
+          <t>4D SOFTWARE LIMITED</t>
         </is>
       </c>
       <c r="B290">
-        <v>13.9</v>
+        <v>0.0</v>
       </c>
       <c r="C290">
-        <v>35.9</v>
+        <v>21.0</v>
       </c>
       <c r="D290">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -23461,43 +23461,43 @@
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-filling-stations-dublin/watch_note.md</t>
+          <t>ic_packs/cro-406809/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Profitable And High Potential Natural Juices Business Ireland</t>
+          <t>A &amp; M. DISTRIBUTORS LIMITED</t>
         </is>
       </c>
       <c r="B291">
-        <v>13.9</v>
+        <v>0.0</v>
       </c>
       <c r="C291">
-        <v>35.9</v>
+        <v>23.1</v>
       </c>
       <c r="D291">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -23507,27 +23507,27 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
@@ -23542,33 +23542,33 @@
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-profitable-and-high-potential-natural-juices-business-ireland-dublin/watch_note.md</t>
+          <t>ic_packs/cro-226593/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>A.P. MCCARTHY PLANNING CONSULTANTS LIMITED</t>
+          <t>A &amp; P AVIATION LIMITED</t>
         </is>
       </c>
       <c r="B292">
-        <v>13.7</v>
+        <v>0.0</v>
       </c>
       <c r="C292">
-        <v>35.7</v>
+        <v>23.1</v>
       </c>
       <c r="D292">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -23583,12 +23583,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -23608,7 +23608,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -23623,33 +23623,33 @@
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>ic_packs/cro-328511/watch_note.md</t>
+          <t>ic_packs/cro-189250/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>A. M. S. ENGINEERING COMPANY LIMITED</t>
+          <t>A J D DEVELOPMENTS LIMITED</t>
         </is>
       </c>
       <c r="B293">
-        <v>12.3</v>
+        <v>0.0</v>
       </c>
       <c r="C293">
-        <v>34.3</v>
+        <v>21.0</v>
       </c>
       <c r="D293">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -23664,12 +23664,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -23689,7 +23689,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -23704,73 +23704,73 @@
       </c>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>ic_packs/cro-28525/watch_note.md</t>
+          <t>ic_packs/cro-328171/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Surveillance Device Sales Partner Opportunity</t>
+          <t>A. B. C. CUISINES LIMITED</t>
         </is>
       </c>
       <c r="B294">
-        <v>11.6</v>
+        <v>0.0</v>
       </c>
       <c r="C294">
-        <v>33.6</v>
+        <v>23.1</v>
       </c>
       <c r="D294">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -23785,33 +23785,33 @@
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-surveillance-device-sales-partner-opportunity-ireland/watch_note.md</t>
+          <t>ic_packs/cro-58944/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>A &amp; D; ADVERTISING AND DESIGN CONSULTANTS LIMITED</t>
+          <t>A. G. FEED LIMITED</t>
         </is>
       </c>
       <c r="B295">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="C295">
-        <v>33.0</v>
+        <v>23.1</v>
       </c>
       <c r="D295">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -23826,12 +23826,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
@@ -23866,33 +23866,33 @@
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>ic_packs/cro-234849/watch_note.md</t>
+          <t>ic_packs/cro-347425/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>A LEONARD MANAGEMENT &amp; CONSULTING LIMITED</t>
+          <t>A. K. D. LIMITED</t>
         </is>
       </c>
       <c r="B296">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="C296">
-        <v>33.0</v>
+        <v>23.1</v>
       </c>
       <c r="D296">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -23907,12 +23907,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
@@ -23947,33 +23947,33 @@
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>ic_packs/cro-481667/watch_note.md</t>
+          <t>ic_packs/cro-75533/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>GROUNDSOURCE LIMITED</t>
+          <t>A. LOOK LIMITED</t>
         </is>
       </c>
       <c r="B297">
-        <v>10.1</v>
+        <v>0.0</v>
       </c>
       <c r="C297">
-        <v>32.1</v>
+        <v>23.1</v>
       </c>
       <c r="D297">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -23988,12 +23988,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -24013,7 +24013,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -24028,43 +24028,43 @@
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>ic_packs/cro-385921/watch_note.md</t>
+          <t>ic_packs/cro-322344/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>KD ECO+ Laminates - Services Franchise in Dublin</t>
+          <t>A. O'TOOLE (CONFECTIONERS) LIMITED</t>
         </is>
       </c>
       <c r="B298">
-        <v>9.7</v>
+        <v>0.0</v>
       </c>
       <c r="C298">
-        <v>31.7</v>
+        <v>24.4</v>
       </c>
       <c r="D298">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -24074,27 +24074,27 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -24109,38 +24109,38 @@
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-kd-eco-laminates-services-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-72100/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>KD ECO+ Laminates - Services Franchise in Galway</t>
+          <t>A.1. DEV CHIMNEY CO. LIMITED</t>
         </is>
       </c>
       <c r="B299">
-        <v>9.7</v>
+        <v>0.0</v>
       </c>
       <c r="C299">
-        <v>31.7</v>
+        <v>23.1</v>
       </c>
       <c r="D299">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -24155,27 +24155,27 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -24190,33 +24190,33 @@
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-kd-eco-laminates-services-franchise-in-galway-galway/watch_note.md</t>
+          <t>ic_packs/cro-346214/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>A.E.D. SECURITY INSTALLATIONS LIMITED</t>
+          <t>A.B.V.G. (A BRIGHTER VISION GENERALLY) LIMITED</t>
         </is>
       </c>
       <c r="B300">
-        <v>8.4</v>
+        <v>0.0</v>
       </c>
       <c r="C300">
-        <v>30.4</v>
+        <v>23.1</v>
       </c>
       <c r="D300">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -24231,12 +24231,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Facilities Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24256,7 +24256,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -24271,73 +24271,73 @@
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>ic_packs/cro-359827/watch_note.md</t>
+          <t>ic_packs/cro-465159/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>High End Pizza Franchise - Only €5,000</t>
+          <t>A.E.R. LIMITED</t>
         </is>
       </c>
       <c r="B301">
-        <v>7.6</v>
+        <v>0.0</v>
       </c>
       <c r="C301">
-        <v>29.6</v>
+        <v>23.1</v>
       </c>
       <c r="D301">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
@@ -24352,43 +24352,43 @@
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-high-end-pizza-franchise-only-5-000-dublin/watch_note.md</t>
+          <t>ic_packs/cro-240545/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Gym Franchise Opportunity</t>
+          <t>A.M. &amp; D. HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="B302">
-        <v>7.2</v>
+        <v>0.0</v>
       </c>
       <c r="C302">
-        <v>29.2</v>
+        <v>21.0</v>
       </c>
       <c r="D302">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -24398,27 +24398,27 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
@@ -24433,43 +24433,43 @@
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-gym-franchise-opportunity-ireland/watch_note.md</t>
+          <t>ic_packs/cro-217915/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Best.Energy - Energy Monitoring Franchise in Dublin</t>
+          <t>A.M. &amp; D. LIMITED</t>
         </is>
       </c>
       <c r="B303">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="C303">
-        <v>29.0</v>
+        <v>23.1</v>
       </c>
       <c r="D303">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -24479,27 +24479,27 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -24514,38 +24514,38 @@
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-best-energy-energy-monitoring-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-214417/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Franchise Pizzeria Restaurant l 3 Bed Apartment Galway</t>
+          <t>A.M.T. GALWAY LIMITED</t>
         </is>
       </c>
       <c r="B304">
-        <v>6.7</v>
+        <v>0.0</v>
       </c>
       <c r="C304">
-        <v>28.7</v>
+        <v>23.1</v>
       </c>
       <c r="D304">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -24555,32 +24555,32 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -24595,73 +24595,73 @@
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-franchise-pizzeria-restaurant-l-3-bed-apartment-galway-galway/watch_note.md</t>
+          <t>ic_packs/cro-162537/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>(NEW AGE OFFICE FURNITURE LIMITED) TROSCAN OIFIGE NA H'AOISE NUA TEORANTA</t>
+          <t>Bonordic in Dublin</t>
         </is>
       </c>
       <c r="B305">
-        <v>6.4</v>
+        <v>0.0</v>
       </c>
       <c r="C305">
-        <v>28.4</v>
+        <v>23.6</v>
       </c>
       <c r="D305">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -24676,33 +24676,33 @@
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>ic_packs/cro-154946/watch_note.md</t>
+          <t>ic_packs/name-county-bonordic-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Multi-Site Fitness Franchise Portfolio – Ireland</t>
+          <t>Brian Tracy Solutions Leadership &amp; Sales Training Consultancy in Galway</t>
         </is>
       </c>
       <c r="B306">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="C306">
-        <v>27.0</v>
+        <v>23.6</v>
       </c>
       <c r="D306">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -24722,7 +24722,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -24757,33 +24757,33 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-multi-site-fitness-franchise-portfolio-ireland-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-brian-tracy-solutions-leadership-sales-training-consultancy-in-galway-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Evoglide Automotive Franchise in Dublin</t>
+          <t>Brian Tracy Solutions Leadership &amp; Sales Training Consultancy in Swords</t>
         </is>
       </c>
       <c r="B307">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C307">
-        <v>26.3</v>
+        <v>23.6</v>
       </c>
       <c r="D307">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -24803,7 +24803,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -24838,33 +24838,33 @@
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-evoglide-automotive-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-brian-tracy-solutions-leadership-sales-training-consultancy-in-swords-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Four Star Pizza in Balbriggan</t>
+          <t>Energie fitness in Dublin</t>
         </is>
       </c>
       <c r="B308">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C308">
-        <v>26.3</v>
+        <v>23.6</v>
       </c>
       <c r="D308">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -24919,33 +24919,33 @@
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-four-star-pizza-in-balbriggan-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-energie-fitness-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Gecko Hospitality Recruitment Franchise in Dublin</t>
+          <t>Energie fitness in Swords</t>
         </is>
       </c>
       <c r="B309">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C309">
-        <v>26.3</v>
+        <v>23.6</v>
       </c>
       <c r="D309">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -24965,7 +24965,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25000,43 +25000,43 @@
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-gecko-hospitality-recruitment-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-energie-fitness-in-swords-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Signarama International Master Franchise Opportunities</t>
+          <t>GARDEN LEISURE PRODUCTS LIMITED/TROSCAN GHAIRDINI TEORANTA</t>
         </is>
       </c>
       <c r="B310">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C310">
-        <v>26.3</v>
+        <v>23.1</v>
       </c>
       <c r="D310">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -25046,27 +25046,27 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -25081,43 +25081,43 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-signarama-international-master-franchise-opportunities-dublin/watch_note.md</t>
+          <t>ic_packs/cro-157217/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Specialist Glass Repairs - Glass &amp; Acrylic Repair Franchise in Dublin</t>
+          <t>GARDEN PRIDE TOOL HIRE LIMITED</t>
         </is>
       </c>
       <c r="B311">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C311">
-        <v>26.3</v>
+        <v>23.1</v>
       </c>
       <c r="D311">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -25127,27 +25127,27 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -25162,43 +25162,43 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-specialist-glass-repairs-glass-acrylic-repair-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-369982/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>WeddingBox Event Planning Franchise in Dublin</t>
+          <t>LAWN RANGER LIMITED</t>
         </is>
       </c>
       <c r="B312">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C312">
-        <v>26.3</v>
+        <v>23.1</v>
       </c>
       <c r="D312">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -25208,27 +25208,27 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -25243,73 +25243,73 @@
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-weddingbox-event-planning-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-345282/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>GARDEN GREEN ENERGY LIMITED</t>
+          <t>Young Engineers Franchise in Dublin</t>
         </is>
       </c>
       <c r="B313">
-        <v>3.8</v>
+        <v>0.0</v>
       </c>
       <c r="C313">
-        <v>25.8</v>
+        <v>23.6</v>
       </c>
       <c r="D313">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -25324,7 +25324,7 @@
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>ic_packs/cro-463334/watch_note.md</t>
+          <t>ic_packs/name-county-young-engineers-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
